--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/enerji_isletme.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/enerji_isletme.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>70,00 m³/saat</t>
+          <t>7.571,00 m³/saat</t>
         </is>
       </c>
       <c r="C2" s="6" t="n"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>13,00 Kuruş</t>
+          <t>13,00 € cent</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
@@ -1004,7 +1004,7 @@
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
@@ -1026,7 +1026,7 @@
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -1054,15 +1054,15 @@
       </c>
       <c r="H13" s="32" t="inlineStr">
         <is>
-          <t>₺ / gün
-₺ / yıl</t>
+          <t>€ / gün
+€ / yıl</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>*** "1 kW/saat = 13 Kuruş" TÜRKİYE şartları baz alınmış olup karşılaştırma amaçlıdır.</t>
+          <t>*** "1 kW/saat = 13 € cent" TÜRKİYE şartları baz alınmış olup karşılaştırma amaçlıdır.</t>
         </is>
       </c>
     </row>
